--- a/2026.xlsx
+++ b/2026.xlsx
@@ -815,7 +815,11 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>-</t>
@@ -932,7 +936,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -940,7 +944,11 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>-</t>
@@ -1057,7 +1065,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1333,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2228,7 +2236,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2615,7 +2623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -1589,11 +1589,7 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1718,11 +1714,7 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>-</t>
@@ -1847,11 +1839,7 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>X</t>
@@ -2105,11 +2093,7 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>-</t>
@@ -2236,7 +2220,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2355,7 +2339,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2607,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2742,7 +2726,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
     </row>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -1589,7 +1589,11 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1714,7 +1718,11 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>-</t>
@@ -1839,7 +1847,11 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>X</t>
@@ -2093,7 +2105,11 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>-</t>
@@ -2220,7 +2236,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2339,7 +2355,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2726,7 +2742,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Veikko Saarela</t>
+          <t>Cristiano Federico Sandon</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
     </row>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Cristiano Federico Sandon</t>
+          <t>Veikko Saarela</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -413,25 +413,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA183"/>
+  <dimension ref="A1:X183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>SELECTION 1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SELECTION 2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>KATALOG-NR</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SELECTION 1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>SELECTION 2</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>CHIP-NUMMER</t>
@@ -535,37 +535,22 @@
       <c r="X1" t="inlineStr">
         <is>
           <t>RICHTER TAG 2</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>KLASSE_INTERNAL</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>KAT_STR</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>SELECTION</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -668,33 +653,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,33 +769,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,33 +885,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,33 +1001,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,33 +1117,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,33 +1233,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,33 +1349,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,33 +1465,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y9" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,33 +1581,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,33 +1697,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,33 +1813,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,33 +1929,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,33 +2045,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y14" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,33 +2161,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y15" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,33 +2277,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y16" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2603,33 +2393,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y17" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2732,33 +2509,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y18" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,33 +2625,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2990,33 +2741,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3119,33 +2857,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y21" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3248,33 +2973,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y22" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3377,33 +3089,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y23" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3506,33 +3205,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3635,33 +3321,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y25" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3764,33 +3437,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y26" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3893,33 +3553,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y27" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4022,33 +3669,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y28" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4151,33 +3785,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y29" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4280,33 +3901,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y30" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4409,33 +4017,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y31" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4538,33 +4133,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y32" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4667,33 +4249,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y33" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
         <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4796,33 +4365,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y34" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4925,33 +4481,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y35" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5054,33 +4597,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y36" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5183,33 +4713,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y37" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
         <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5312,33 +4829,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y38" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
         <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5441,33 +4945,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y39" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
         <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5570,33 +5061,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y40" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5699,33 +5177,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y41" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
         <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5828,33 +5293,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
         <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5957,33 +5409,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y43" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
         <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6086,33 +5525,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y44" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
         <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6215,33 +5641,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y45" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
         <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6344,33 +5757,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y46" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
         <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6473,33 +5873,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y47" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
         <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6602,33 +5989,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y48" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
         <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6731,33 +6105,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y49" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
         <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6860,33 +6221,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y50" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
         <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6989,33 +6337,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y51" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
         <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7118,33 +6453,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y52" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
         <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7247,33 +6569,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y53" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7376,33 +6685,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y54" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
         <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7505,33 +6801,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y55" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
         <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7634,33 +6917,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y56" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
         <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7763,33 +7033,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y57" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
         <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7892,33 +7149,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y58" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
         <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8021,33 +7265,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y59" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
         <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8150,33 +7381,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y60" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
         <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8279,33 +7497,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y61" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
         <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8408,33 +7613,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y62" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
         <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8537,33 +7729,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y63" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
         <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8666,33 +7845,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y64" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
         <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8795,33 +7961,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y65" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
         <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8924,33 +8077,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y66" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
         <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9053,33 +8193,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y67" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
         <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9182,33 +8309,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y68" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
         <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9311,33 +8425,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y69" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
         <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9440,33 +8541,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
         <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9569,33 +8657,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y71" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
         <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9698,33 +8773,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y72" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
         <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9827,33 +8889,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y73" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
         <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9956,33 +9005,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y74" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
         <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10085,33 +9121,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y75" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
         <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10214,33 +9237,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y76" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
         <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10343,33 +9353,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y77" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
         <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10472,33 +9469,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y78" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
         <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10601,33 +9585,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
         <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10730,33 +9701,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y80" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
         <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10859,33 +9817,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y81" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
         <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10988,33 +9933,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y82" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
         <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11117,33 +10049,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y83" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
         <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11246,33 +10165,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y84" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
         <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11375,33 +10281,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y85" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
         <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11504,33 +10397,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y86" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
         <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11633,33 +10513,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y87" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
         <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11762,33 +10629,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y88" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
         <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11891,33 +10745,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y89" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
         <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12020,33 +10861,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y90" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
         <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12149,33 +10977,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y91" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
         <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12278,33 +11093,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y92" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
         <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12407,33 +11209,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y93" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
         <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12536,33 +11325,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y94" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
         <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12665,33 +11441,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y95" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
         <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12794,33 +11557,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y96" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
         <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12923,33 +11673,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y97" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
         <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13052,33 +11789,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y98" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
         <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13181,33 +11905,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y99" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
         <v>99</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13310,33 +12021,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y100" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
         <v>100</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13439,33 +12137,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y101" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
         <v>101</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13568,33 +12253,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y102" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
         <v>102</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13697,33 +12369,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y103" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
         <v>103</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13826,33 +12485,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y104" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
         <v>104</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13955,33 +12601,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y105" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
         <v>105</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14084,33 +12717,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y106" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
         <v>106</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14213,33 +12833,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y107" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
         <v>107</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14342,33 +12949,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y108" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
         <v>108</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14471,33 +13065,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y109" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
         <v>109</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14600,33 +13181,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y110" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
         <v>110</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14729,33 +13297,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y111" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
         <v>111</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14858,33 +13413,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y112" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
         <v>112</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14987,33 +13529,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y113" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
         <v>113</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15116,33 +13645,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y114" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
         <v>114</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15245,33 +13761,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y115" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
         <v>115</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15374,33 +13877,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y116" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
         <v>116</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15503,33 +13993,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y117" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
         <v>117</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15632,33 +14109,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y118" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
         <v>118</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15761,33 +14225,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y119" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
         <v>119</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15890,33 +14341,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y120" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
         <v>120</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16019,33 +14457,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y121" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
         <v>121</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16148,33 +14573,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y122" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
         <v>122</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16277,33 +14689,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y123" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
         <v>123</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16406,33 +14805,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y124" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
         <v>124</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16535,33 +14921,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y125" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
         <v>125</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -16664,33 +15037,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y126" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
         <v>126</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16793,33 +15153,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y127" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
         <v>127</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16922,33 +15269,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y128" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
         <v>128</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -17051,33 +15385,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y129" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
         <v>129</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17180,33 +15501,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y130" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
         <v>130</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -17309,33 +15617,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y131" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
         <v>131</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -17438,33 +15733,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y132" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
         <v>132</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -17567,33 +15849,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y133" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
         <v>133</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17696,33 +15965,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y134" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
         <v>134</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17825,33 +16081,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y135" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
         <v>135</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17954,33 +16197,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y136" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
         <v>136</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18083,33 +16313,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y137" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
         <v>137</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18212,33 +16429,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y138" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
         <v>138</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18341,33 +16545,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y139" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
         <v>139</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -18470,33 +16661,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y140" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
         <v>140</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -18599,33 +16777,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y141" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
         <v>141</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18728,33 +16893,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y142" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="143">
-      <c r="A143" t="n">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
         <v>142</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18857,33 +17009,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y143" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="144">
-      <c r="A144" t="n">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
         <v>143</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18986,33 +17125,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y144" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="145">
-      <c r="A145" t="n">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
         <v>144</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -19115,33 +17241,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y145" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="146">
-      <c r="A146" t="n">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
         <v>145</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19244,33 +17357,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y146" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="147">
-      <c r="A147" t="n">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
         <v>146</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19373,33 +17473,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y147" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
         <v>147</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -19502,33 +17589,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y148" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="149">
-      <c r="A149" t="n">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
         <v>148</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -19631,33 +17705,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y149" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
         <v>149</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -19760,33 +17821,20 @@
           <t>Gerardo Fraga y Guzman</t>
         </is>
       </c>
-      <c r="Y150" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="151">
-      <c r="A151" t="n">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
         <v>150</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -19889,33 +17937,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y151" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
         <v>151</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -20018,33 +18053,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y152" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
         <v>152</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -20147,33 +18169,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y153" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
         <v>153</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -20276,33 +18285,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y154" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
         <v>154</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -20405,33 +18401,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y155" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
         <v>155</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -20534,33 +18517,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y156" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
         <v>156</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -20663,33 +18633,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y157" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
         <v>157</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -20792,33 +18749,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y158" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
         <v>158</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -20921,33 +18865,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y159" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
         <v>159</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -21050,33 +18981,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y160" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
         <v>160</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21179,33 +19097,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y161" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
         <v>161</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21308,33 +19213,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y162" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
         <v>162</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21437,33 +19329,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y163" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
         <v>163</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -21566,33 +19445,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y164" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="165">
-      <c r="A165" t="n">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
         <v>164</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -21695,33 +19561,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y165" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
         <v>165</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -21824,33 +19677,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y166" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="167">
-      <c r="A167" t="n">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
         <v>166</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -21953,33 +19793,20 @@
           <t>Martti Peltonen</t>
         </is>
       </c>
-      <c r="Y167" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
         <v>167</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -22082,33 +19909,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y168" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="169">
-      <c r="A169" t="n">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
         <v>168</v>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -22211,33 +20025,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y169" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
         <v>169</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -22340,33 +20141,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y170" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
         <v>170</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -22469,33 +20257,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y171" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
         <v>171</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -22598,33 +20373,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y172" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="173">
-      <c r="A173" t="n">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
         <v>172</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -22727,33 +20489,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y173" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="174">
-      <c r="A174" t="n">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
         <v>173</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -22856,33 +20605,20 @@
           <t>Cristiano Federico Sandon</t>
         </is>
       </c>
-      <c r="Y174" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="175">
-      <c r="A175" t="n">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
         <v>174</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -22985,33 +20721,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y175" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="176">
-      <c r="A176" t="n">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
         <v>175</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -23114,33 +20837,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y176" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="177">
-      <c r="A177" t="n">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
         <v>176</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -23243,33 +20953,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y177" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="178">
-      <c r="A178" t="n">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
         <v>177</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -23372,33 +21069,20 @@
           <t>Veikko Saarela</t>
         </is>
       </c>
-      <c r="Y178" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="179">
-      <c r="A179" t="n">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
         <v>178</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -23501,33 +21185,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y179" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
         <v>179</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -23630,33 +21301,20 @@
           <t>Jørgen Billing</t>
         </is>
       </c>
-      <c r="Y180" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
     </row>
     <row r="181">
-      <c r="A181" t="n">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
         <v>180</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -23759,33 +21417,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y181" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="182">
-      <c r="A182" t="n">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
         <v>181</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -23888,33 +21533,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y182" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="183">
-      <c r="A183" t="n">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
         <v>182</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -24013,19 +21645,6 @@
         </is>
       </c>
       <c r="X183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y183" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -889,7 +889,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -889,7 +889,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -549,8 +549,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,8 +667,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,8 +785,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,8 +903,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,8 +1021,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>5</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,8 +1139,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>6</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,8 +1257,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>7</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,8 +1375,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>8</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,8 +1493,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>9</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,8 +1611,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>10</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,8 +1729,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>11</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,8 +1847,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>12</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,8 +1965,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>13</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,8 +2083,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>14</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,8 +2201,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>15</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,8 +2319,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>16</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,8 +2437,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>17</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,8 +2555,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>18</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,8 +2673,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>19</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,8 +2791,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>20</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,8 +2909,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>21</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2985,8 +3027,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>22</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,8 +3145,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>23</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3217,8 +3263,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>24</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3333,8 +3381,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>25</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3449,8 +3499,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>26</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,8 +3617,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>27</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,8 +3735,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>28</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,8 +3853,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>29</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3913,8 +3971,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>30</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4029,8 +4089,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>31</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,8 +4207,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>32</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,8 +4325,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>33</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4377,8 +4443,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>34</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,8 +4561,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>35</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4609,8 +4679,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>36</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4725,8 +4797,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>37</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,8 +4915,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>38</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4957,8 +5033,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>39</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5073,8 +5151,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>40</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5189,8 +5269,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>41</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,8 +5387,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>42</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5421,8 +5505,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>43</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5537,8 +5623,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>44</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5653,8 +5741,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>45</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5769,8 +5859,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>46</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5885,8 +5977,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>47</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6001,8 +6095,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>48</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6117,8 +6213,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>49</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,8 +6331,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>50</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6349,8 +6449,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>51</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6465,8 +6567,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>52</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6581,8 +6685,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>53</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6697,8 +6803,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>54</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6813,8 +6921,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>55</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6929,8 +7039,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>56</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7045,8 +7157,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>57</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7161,8 +7275,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>58</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7277,8 +7393,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>59</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7393,8 +7511,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>60</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7509,8 +7629,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>61</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7625,8 +7747,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>62</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7741,8 +7865,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>63</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7857,8 +7983,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>64</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7973,8 +8101,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>65</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8089,8 +8219,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>66</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8205,8 +8337,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>67</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8321,8 +8455,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>68</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8437,8 +8573,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>69</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8553,8 +8691,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>70</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8669,8 +8809,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>71</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8785,8 +8927,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>72</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8901,8 +9045,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>73</v>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9017,8 +9163,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>74</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9133,8 +9281,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>75</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9249,8 +9399,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>76</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9365,8 +9517,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>77</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9481,8 +9635,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>78</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9597,8 +9753,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>79</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9713,8 +9871,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>80</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9829,8 +9989,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>81</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9945,8 +10107,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>82</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10061,8 +10225,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>83</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10177,8 +10343,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>84</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10293,8 +10461,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>85</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10409,8 +10579,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>86</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10525,8 +10697,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>87</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10641,8 +10815,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>88</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10757,8 +10933,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>89</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10873,8 +11051,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C91" t="n">
-        <v>90</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10989,8 +11169,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v>91</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11105,8 +11287,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C93" t="n">
-        <v>92</v>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11221,8 +11405,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>93</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11337,8 +11523,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>94</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11453,8 +11641,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>95</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11569,8 +11759,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>96</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11685,8 +11877,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>97</v>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11801,8 +11995,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>98</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11917,8 +12113,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>99</v>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12033,8 +12231,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C101" t="n">
-        <v>100</v>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12149,8 +12349,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>101</v>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12265,8 +12467,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>102</v>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12381,8 +12585,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>103</v>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12497,8 +12703,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>104</v>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12613,8 +12821,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>105</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12729,8 +12939,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C107" t="n">
-        <v>106</v>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12845,8 +13057,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>107</v>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12961,8 +13175,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C109" t="n">
-        <v>108</v>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13077,8 +13293,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>109</v>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13193,8 +13411,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>110</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13309,8 +13529,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>111</v>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13425,8 +13647,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C113" t="n">
-        <v>112</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13541,8 +13765,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v>113</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13657,8 +13883,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>114</v>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13773,8 +14001,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C116" t="n">
-        <v>115</v>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13889,8 +14119,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>116</v>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14005,8 +14237,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C118" t="n">
-        <v>117</v>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14121,8 +14355,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C119" t="n">
-        <v>118</v>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14237,8 +14473,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v>119</v>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14353,8 +14591,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C121" t="n">
-        <v>120</v>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14469,8 +14709,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>121</v>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14585,8 +14827,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C123" t="n">
-        <v>122</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14701,8 +14945,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v>123</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14817,8 +15063,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C125" t="n">
-        <v>124</v>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14933,8 +15181,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v>125</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15049,8 +15299,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C127" t="n">
-        <v>126</v>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15165,8 +15417,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C128" t="n">
-        <v>127</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15281,8 +15535,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C129" t="n">
-        <v>128</v>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15397,8 +15653,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C130" t="n">
-        <v>129</v>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15513,8 +15771,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C131" t="n">
-        <v>130</v>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15629,8 +15889,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v>131</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15745,8 +16007,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C133" t="n">
-        <v>132</v>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15861,8 +16125,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C134" t="n">
-        <v>133</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15977,8 +16243,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C135" t="n">
-        <v>134</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16093,8 +16361,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>135</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16209,8 +16479,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C137" t="n">
-        <v>136</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16325,8 +16597,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C138" t="n">
-        <v>137</v>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16441,8 +16715,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C139" t="n">
-        <v>138</v>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16557,8 +16833,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v>139</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16673,8 +16951,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C141" t="n">
-        <v>140</v>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16789,8 +17069,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>141</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16905,8 +17187,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C143" t="n">
-        <v>142</v>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17021,8 +17305,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C144" t="n">
-        <v>143</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17137,8 +17423,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C145" t="n">
-        <v>144</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17253,8 +17541,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C146" t="n">
-        <v>145</v>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17369,8 +17659,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C147" t="n">
-        <v>146</v>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17485,8 +17777,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C148" t="n">
-        <v>147</v>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17601,8 +17895,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C149" t="n">
-        <v>148</v>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17717,8 +18013,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C150" t="n">
-        <v>149</v>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17833,8 +18131,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C151" t="n">
-        <v>150</v>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17949,8 +18249,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C152" t="n">
-        <v>151</v>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18065,8 +18367,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C153" t="n">
-        <v>152</v>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18181,8 +18485,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v>153</v>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18297,8 +18603,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C155" t="n">
-        <v>154</v>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18413,8 +18721,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C156" t="n">
-        <v>155</v>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18529,8 +18839,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C157" t="n">
-        <v>156</v>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18645,8 +18957,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>157</v>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18761,8 +19075,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C159" t="n">
-        <v>158</v>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18877,8 +19193,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C160" t="n">
-        <v>159</v>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18993,8 +19311,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C161" t="n">
-        <v>160</v>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19109,8 +19429,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C162" t="n">
-        <v>161</v>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19225,8 +19547,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C163" t="n">
-        <v>162</v>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19341,8 +19665,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C164" t="n">
-        <v>163</v>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19457,8 +19783,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C165" t="n">
-        <v>164</v>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19573,8 +19901,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C166" t="n">
-        <v>165</v>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19689,8 +20019,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C167" t="n">
-        <v>166</v>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19805,8 +20137,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C168" t="n">
-        <v>167</v>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19921,8 +20255,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C169" t="n">
-        <v>168</v>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20037,8 +20373,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C170" t="n">
-        <v>169</v>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20153,8 +20491,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C171" t="n">
-        <v>170</v>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20269,8 +20609,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C172" t="n">
-        <v>171</v>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20385,8 +20727,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C173" t="n">
-        <v>172</v>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20501,8 +20845,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C174" t="n">
-        <v>173</v>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20617,8 +20963,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C175" t="n">
-        <v>174</v>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20733,8 +21081,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C176" t="n">
-        <v>175</v>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20849,8 +21199,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C177" t="n">
-        <v>176</v>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20965,8 +21317,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C178" t="n">
-        <v>177</v>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21081,8 +21435,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C179" t="n">
-        <v>178</v>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21197,8 +21553,10 @@
           <t>X</t>
         </is>
       </c>
-      <c r="C180" t="n">
-        <v>179</v>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21313,8 +21671,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C181" t="n">
-        <v>180</v>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21429,8 +21789,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C182" t="n">
-        <v>181</v>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21545,8 +21907,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C183" t="n">
-        <v>182</v>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -777,7 +777,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -1131,7 +1131,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -895,7 +895,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -1013,7 +1013,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t xml:space="preserve">X </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1131,7 +1131,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -1013,7 +1013,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">X </t>
+          <t>X</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t xml:space="preserve">X </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>d 03 22</t>
+          <t>ds 03 22</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -777,7 +777,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -777,7 +777,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ds 03 22</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -7149,7 +7149,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7267,7 +7267,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
